--- a/data/测试用例_200条_fix.xlsx
+++ b/data/测试用例_200条_fix.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="15980" windowHeight="18240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -696,7 +696,7 @@
     <t>/api/uploads/image</t>
   </si>
   <si>
-    <t>{"file":("test.jpg", open("data/test.jpg","rb"), "image/jpeg")}</t>
+    <t>{"file":("test.jpg", "data/test.jpg", "image/jpeg")}</t>
   </si>
   <si>
     <t>上传成功</t>
@@ -1521,7 +1521,7 @@
     <t>上传图片-非图片文件</t>
   </si>
   <si>
-    <t>{"file":("test.txt", open("data/test.txt","rb"), "text/plain")}</t>
+    <t>{"file":("test.txt", "data/test.txt", "text/plain")}</t>
   </si>
   <si>
     <t>上传图片-成功DB校验</t>
@@ -1581,7 +1581,7 @@
     <t>上传图片-空文件</t>
   </si>
   <si>
-    <t>{"file":("empty.jpg", open("data/empty.jpg","rb"), "image/jpeg")}</t>
+    <t>{"file":("empty.jpg", "data/empty.jpg", "image/jpeg")}</t>
   </si>
 </sst>
 </file>
